--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487956_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487956_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5488</v>
+        <v>9.815899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2015</v>
+        <v>7.6089</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3473</v>
+        <v>2.2069</v>
       </c>
       <c r="G2" t="n">
         <v>6.4127</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5414</v>
+        <v>0.8085</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.4737</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4752</v>
+        <v>0.3348</v>
       </c>
       <c r="V2" t="n">
         <v>1.2071</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9874</v>
+        <v>8.489599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>4.627</v>
+        <v>4.9326</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3604</v>
+        <v>3.557</v>
       </c>
       <c r="G3" t="n">
         <v>8.064</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5591</v>
+        <v>-0.057</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4992</v>
+        <v>-0.1936</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0599</v>
+        <v>0.1366</v>
       </c>
       <c r="V3" t="n">
         <v>1.4737</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8883</v>
+        <v>7.6262</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1155</v>
+        <v>6.1342</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7728</v>
+        <v>1.492</v>
       </c>
       <c r="G4" t="n">
         <v>4.8878</v>
@@ -766,13 +766,13 @@
         <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2165</v>
+        <v>0.9544</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6129</v>
+        <v>0.4058</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8294</v>
+        <v>0.5486</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8738</v>
+        <v>5.1398</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4706</v>
+        <v>0.9613</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4032</v>
+        <v>4.1785</v>
       </c>
       <c r="G5" t="n">
         <v>3.711</v>
@@ -844,13 +844,13 @@
         <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5791</v>
+        <v>0.8451</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9072</v>
+        <v>0.6826</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4074</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6398</v>
+        <v>4.2781</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1876</v>
+        <v>-0.4932</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8275</v>
+        <v>4.7713</v>
       </c>
       <c r="G6" t="n">
         <v>4.2457</v>
@@ -922,13 +922,13 @@
         <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7113</v>
+        <v>0.3496</v>
       </c>
       <c r="T6" t="n">
-        <v>0.18</v>
+        <v>-0.1257</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5314</v>
+        <v>0.4752</v>
       </c>
       <c r="V6" t="n">
         <v>0.674</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0006</v>
+        <v>2.6555</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3145</v>
+        <v>2.1627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6861</v>
+        <v>0.4928</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9639</v>
+        <v>0.9357</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6806</v>
+        <v>0.8706</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2833</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5404</v>
+        <v>2.3856</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0025</v>
+        <v>1.5341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5379</v>
+        <v>0.8515</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5765</v>
+        <v>-1.4499</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3219</v>
+        <v>-0.6634</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2545</v>
+        <v>-0.7864</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4331</v>
+        <v>1.1251</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5492</v>
+        <v>0.7682</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1161</v>
+        <v>0.3569</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6731</v>
+        <v>2.3999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2646</v>
+        <v>1.6014</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4086</v>
+        <v>0.7984</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9357</v>
+        <v>0.9639</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8706</v>
+        <v>0.6806</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2833</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3856</v>
+        <v>1.5404</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5341</v>
+        <v>1.0025</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8515</v>
+        <v>0.5379</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4499</v>
+        <v>-0.5765</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6634</v>
+        <v>-0.3219</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7864</v>
+        <v>-0.2545</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1428</v>
+        <v>0.8324</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8701</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2727</v>
+        <v>-0.0038</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>M. VIÑUELA URBANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4142</v>
+        <v>1.2053</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9516</v>
+        <v>1.2053</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4626</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8310999999999999</v>
+        <v>1.2053</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2647</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5664</v>
+        <v>1.2053</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0191</v>
+        <v>1.2053</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3425</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3616</v>
+        <v>1.2053</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8502999999999999</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07770000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.928</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9945000000000001</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9325</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0619</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VIÑUELA URBANO</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2053</v>
+        <v>1.1824</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2053</v>
+        <v>0.7479</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.4345</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2053</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.2647</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2053</v>
+        <v>-0.5664</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2053</v>
+        <v>0.0191</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.3425</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2053</v>
+        <v>0.3616</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.928</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.7288</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. VINUELA URBANO</t>
+          <t>N. ALVAREZ ALVAREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0165</v>
+        <v>0.8298</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9416</v>
+        <v>-1.2641</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07489999999999999</v>
+        <v>2.0939</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5981</v>
+        <v>1.3473</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1614</v>
+        <v>1.2574</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7595</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1207</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0404</v>
+        <v>0.5044</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0804</v>
+        <v>-0.5949</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4774</v>
+        <v>1.4378</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2018</v>
+        <v>0.7529</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6791</v>
+        <v>0.6848</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5572</v>
+        <v>0.5598</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5543</v>
+        <v>0.0157</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0029</v>
+        <v>0.5441</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.337</v>
+        <v>-1.4737</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6036</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. ALVAREZ ALVAREZ</t>
+          <t>A. TERNERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7352</v>
+        <v>0.6974</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1622</v>
+        <v>-0.4015</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8974</v>
+        <v>1.0989</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3473</v>
+        <v>1.3895</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2574</v>
+        <v>1.1083</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.2812</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.9724</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5044</v>
+        <v>0.9685</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5949</v>
+        <v>0.0039</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4378</v>
+        <v>0.4171</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7529</v>
+        <v>0.1398</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6848</v>
+        <v>0.2774</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4651</v>
+        <v>-0.3552</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1176</v>
+        <v>-0.0459</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3475</v>
+        <v>-0.3093</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4737</v>
+        <v>-0.337</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. RAGA RODRÍGUEZ</t>
+          <t>M. VINUELA URBANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6027</v>
+        <v>0.6548</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6027</v>
+        <v>0.636</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.0188</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6027</v>
+        <v>0.5981</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.1614</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6027</v>
+        <v>0.7595</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6027</v>
+        <v>0.1207</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6027</v>
+        <v>0.0804</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.4774</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.2018</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.6791</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.1955</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.2487</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TERNERO RODRIGUEZ</t>
+          <t>R. RAGA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3532</v>
+        <v>0.6027</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6052999999999999</v>
+        <v>0.6027</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9585</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3895</v>
+        <v>0.6027</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1083</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2812</v>
+        <v>0.6027</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9724</v>
+        <v>0.6027</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9685</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0039</v>
+        <v>0.6027</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4171</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1398</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2774</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6993</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2496</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4497</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1427</v>
+        <v>-0.781</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2074</v>
+        <v>-0.9018</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1208</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8063</v>
@@ -1702,13 +1702,13 @@
         <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.4395</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3898</v>
+        <v>0.4459</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2071</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>46.0015</v>
+        <v>46.00170000000001</v>
       </c>
       <c r="E17" t="n">
         <v>24.7377</v>
       </c>
       <c r="F17" t="n">
-        <v>21.264</v>
+        <v>21.2638</v>
       </c>
       <c r="G17" t="n">
         <v>33.9316</v>
@@ -1753,7 +1753,7 @@
         <v>19.4382</v>
       </c>
       <c r="J17" t="n">
-        <v>31.9352</v>
+        <v>31.93520000000001</v>
       </c>
       <c r="K17" t="n">
         <v>13.3472</v>
@@ -1780,16 +1780,16 @@
         <v>19.8224</v>
       </c>
       <c r="S17" t="n">
-        <v>6.4604</v>
+        <v>6.4603</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2681</v>
+        <v>3.267999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>3.192300000000001</v>
+        <v>3.1922</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3369000000000002</v>
+        <v>-0.3369</v>
       </c>
       <c r="W17" t="n">
         <v>3.4101</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4011</v>
+        <v>-0.1621</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4341</v>
+        <v>-0.0267</v>
       </c>
       <c r="F19" t="n">
-        <v>0.033</v>
+        <v>-0.1355</v>
       </c>
       <c r="G19" t="n">
         <v>-1.675</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2702</v>
+        <v>-0.0312</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3744</v>
+        <v>0.0331</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1042</v>
+        <v>-0.0643</v>
       </c>
       <c r="V19" t="n">
         <v>1.5441</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SIMON DIAZ</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8991</v>
+        <v>-1.4112</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0197</v>
+        <v>-0.1565</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9188</v>
+        <v>-1.2547</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2365</v>
+        <v>-2.0968</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-1.1688</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.486</v>
+        <v>-0.928</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0269</v>
+        <v>0.3096</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0133</v>
+        <v>0.3096</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2634</v>
+        <v>-2.4064</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7372</v>
+        <v>-1.4784</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5262</v>
+        <v>-0.928</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7338</v>
+        <v>-0.5037</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9839</v>
+        <v>-0.4661</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.25</v>
+        <v>-0.0377</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>A. SIMON DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9591</v>
+        <v>-1.7422</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.7953</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3951</v>
+        <v>-0.9469</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0968</v>
+        <v>-1.2365</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1688</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.928</v>
+        <v>-0.486</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3096</v>
+        <v>0.0269</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3096</v>
+        <v>-0.0133</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4064</v>
+        <v>-1.2634</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4784</v>
+        <v>-0.7372</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.928</v>
+        <v>-0.5262</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0516</v>
+        <v>-0.1092</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8736</v>
+        <v>0.1689</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1781</v>
+        <v>-0.2781</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6151</v>
+        <v>-2.3271</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9911</v>
+        <v>-0.7874</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.624</v>
+        <v>-1.5398</v>
       </c>
       <c r="G22" t="n">
         <v>-1.277</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5275</v>
+        <v>-0.2395</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6284</v>
+        <v>-3.1247</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1751</v>
+        <v>-0.2323</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8036</v>
+        <v>-2.8924</v>
       </c>
       <c r="G23" t="n">
         <v>-4.3004</v>
@@ -2248,13 +2248,13 @@
         <v>1.9822</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0595</v>
+        <v>-0.4368</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0479</v>
+        <v>-0.3596</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0116</v>
+        <v>-0.0772</v>
       </c>
       <c r="V23" t="n">
         <v>1.8107</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8652</v>
+        <v>-3.4473</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6677</v>
+        <v>-4.3621</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8025</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1267</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3619</v>
+        <v>0.056</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>-0.1312</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1872</v>
       </c>
       <c r="V24" t="n">
         <v>0.4074</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5415</v>
+        <v>-4.3657</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8522</v>
+        <v>-1.5302</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6892</v>
+        <v>-2.8356</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4644</v>
+        <v>-2.6076</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1245</v>
+        <v>-1.7485</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.3399</v>
+        <v>-0.859</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2812</v>
+        <v>-0.0789</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.0083</v>
+        <v>-0.0064</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7271</v>
+        <v>-0.0726</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.1832</v>
+        <v>-2.5286</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1162</v>
+        <v>-1.7422</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.067</v>
+        <v>-0.7864</v>
       </c>
       <c r="P25" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-1.1893</v>
       </c>
-      <c r="Q25" t="n">
-        <v>-2.1805</v>
-      </c>
       <c r="R25" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1123</v>
+        <v>-1.0159</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6095</v>
+        <v>-0.5285</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4972</v>
+        <v>-0.4874</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.1056</v>
+        <v>-5.1292</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9377</v>
+        <v>-2.4634</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1679</v>
+        <v>-2.6657</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.6076</v>
+        <v>-3.4644</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7485</v>
+        <v>-1.1245</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.859</v>
+        <v>-2.3399</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0789</v>
+        <v>-0.2812</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0064</v>
+        <v>-1.0083</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0726</v>
+        <v>0.7271</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.5286</v>
+        <v>-3.1832</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7422</v>
+        <v>-0.1162</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7864</v>
+        <v>-3.067</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.7557</v>
+        <v>-0.4754</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.0017</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8197</v>
+        <v>-0.4737</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8549</v>
+        <v>-5.5176</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.9172</v>
+        <v>-0.948</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.9376</v>
+        <v>-4.5696</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.6768</v>
+        <v>-4.9762</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.9567</v>
+        <v>-0.9893</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.7201</v>
+        <v>-3.9869</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.2958</v>
+        <v>-0.0561</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.0993</v>
+        <v>0.2018</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8036</v>
+        <v>-0.2579</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.381</v>
+        <v>-4.92</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.191</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.5237</v>
+        <v>-3.729</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="R27" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-1.5325</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5688</v>
+        <v>-0.6936</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2039</v>
+        <v>-0.8389</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.0465</v>
+        <v>-5.6557</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.948</v>
+        <v>-2.7135</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.0986</v>
+        <v>-2.9422</v>
       </c>
       <c r="G28" t="n">
-        <v>-4.9762</v>
+        <v>-5.6768</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9893</v>
+        <v>-3.9567</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.9869</v>
+        <v>-1.7201</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0561</v>
+        <v>-2.2958</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2018</v>
+        <v>-3.0993</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2579</v>
+        <v>0.8036</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.92</v>
+        <v>-3.381</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.191</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.729</v>
+        <v>-2.5237</v>
       </c>
       <c r="P28" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.0615</v>
+        <v>-0.5736</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6936</v>
+        <v>-0.3651</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.3678</v>
+        <v>-0.2085</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="29">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.1763</v>
+        <v>-6.559</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.2885</v>
+        <v>-4.3904</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8878</v>
+        <v>-2.1686</v>
       </c>
       <c r="G29" t="n">
         <v>-1.8499</v>
@@ -2716,13 +2716,13 @@
         <v>0.9911</v>
       </c>
       <c r="S29" t="n">
-        <v>0.312</v>
+        <v>-0.0707</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3816</v>
+        <v>0.1008</v>
       </c>
       <c r="V29" t="n">
         <v>-0.674</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-7.1168</v>
+        <v>-7.0887</v>
       </c>
       <c r="E30" t="n">
         <v>-4.4032</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.7136</v>
+        <v>-2.6855</v>
       </c>
       <c r="G30" t="n">
         <v>-3.8523</v>
@@ -2794,13 +2794,13 @@
         <v>1.1893</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.8769</v>
+        <v>-0.8488</v>
       </c>
       <c r="T30" t="n">
         <v>-0.5688</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.3081</v>
+        <v>-0.28</v>
       </c>
       <c r="V30" t="n">
         <v>-0.6036</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-46.0016</v>
+        <v>-45.32250000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-21.6009</v>
+        <v>-21.601</v>
       </c>
       <c r="F31" t="n">
-        <v>-24.4007</v>
+        <v>-23.7217</v>
       </c>
       <c r="G31" t="n">
         <v>-33.9316</v>
@@ -2872,13 +2872,13 @@
         <v>13.8754</v>
       </c>
       <c r="S31" t="n">
-        <v>-6.4604</v>
+        <v>-5.7813</v>
       </c>
       <c r="T31" t="n">
         <v>-3.1923</v>
       </c>
       <c r="U31" t="n">
-        <v>-3.268</v>
+        <v>-2.5891</v>
       </c>
       <c r="V31" t="n">
         <v>0.3369999999999997</v>
